--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/115.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/115.xlsx
@@ -426,13 +426,13 @@
         <v>-7.966198669796842</v>
       </c>
       <c r="E2">
-        <v>-25.47115133106079</v>
+        <v>-32.05780318979531</v>
       </c>
       <c r="F2">
-        <v>-3.705490489983382</v>
+        <v>-4.752233764243699</v>
       </c>
       <c r="G2">
-        <v>-15.36821565307304</v>
+        <v>-19.01334644308898</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.067266697243817</v>
       </c>
       <c r="E3">
-        <v>-25.67357864767767</v>
+        <v>-32.40634172026966</v>
       </c>
       <c r="F3">
-        <v>-3.73053452167222</v>
+        <v>-4.578694935194217</v>
       </c>
       <c r="G3">
-        <v>-15.51734910852613</v>
+        <v>-18.88934002827896</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.076446025384852</v>
       </c>
       <c r="E4">
-        <v>-25.31577033090961</v>
+        <v>-32.27414424280074</v>
       </c>
       <c r="F4">
-        <v>-3.697481005565714</v>
+        <v>-4.777331639813719</v>
       </c>
       <c r="G4">
-        <v>-15.04215671236468</v>
+        <v>-18.87835067236135</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.971455128570832</v>
       </c>
       <c r="E5">
-        <v>-26.29130778706398</v>
+        <v>-33.20984018463563</v>
       </c>
       <c r="F5">
-        <v>-3.652006948621632</v>
+        <v>-4.668393042671555</v>
       </c>
       <c r="G5">
-        <v>-15.43663138718762</v>
+        <v>-18.52171884359782</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.739562000436835</v>
       </c>
       <c r="E6">
-        <v>-26.61666053061906</v>
+        <v>-32.92825740660169</v>
       </c>
       <c r="F6">
-        <v>-3.668609916475943</v>
+        <v>-4.675357127426891</v>
       </c>
       <c r="G6">
-        <v>-14.81321096977807</v>
+        <v>-18.92607218630994</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.3734514746813</v>
       </c>
       <c r="E7">
-        <v>-27.07975133959145</v>
+        <v>-33.6995448353511</v>
       </c>
       <c r="F7">
-        <v>-3.66394869310039</v>
+        <v>-4.739467794199156</v>
       </c>
       <c r="G7">
-        <v>-14.5965672144154</v>
+        <v>-18.43539140284301</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.876107109267804</v>
       </c>
       <c r="E8">
-        <v>-27.09342733109461</v>
+        <v>-33.40939871296865</v>
       </c>
       <c r="F8">
-        <v>-3.583362627053845</v>
+        <v>-4.488344074203471</v>
       </c>
       <c r="G8">
-        <v>-14.63931959950954</v>
+        <v>-18.0079999737231</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.251605108966944</v>
       </c>
       <c r="E9">
-        <v>-28.18534656924611</v>
+        <v>-34.52636946933058</v>
       </c>
       <c r="F9">
-        <v>-3.52396537080351</v>
+        <v>-4.567071283798134</v>
       </c>
       <c r="G9">
-        <v>-14.25140477067267</v>
+        <v>-18.09540665232371</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.513524283018291</v>
       </c>
       <c r="E10">
-        <v>-28.00057577278515</v>
+        <v>-34.79517742218889</v>
       </c>
       <c r="F10">
-        <v>-3.437257669650277</v>
+        <v>-4.487699604364094</v>
       </c>
       <c r="G10">
-        <v>-14.13558533498127</v>
+        <v>-17.9939847791826</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.692526387571041</v>
       </c>
       <c r="E11">
-        <v>-28.69015368077716</v>
+        <v>-35.20634701242633</v>
       </c>
       <c r="F11">
-        <v>-3.409803088819293</v>
+        <v>-4.439057042104304</v>
       </c>
       <c r="G11">
-        <v>-13.82856534166926</v>
+        <v>-17.50269816588198</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.822179001222834</v>
       </c>
       <c r="E12">
-        <v>-28.71522784135763</v>
+        <v>-35.494851562981</v>
       </c>
       <c r="F12">
-        <v>-3.418160487546138</v>
+        <v>-4.517330306362232</v>
       </c>
       <c r="G12">
-        <v>-13.58164995789549</v>
+        <v>-17.67490777901656</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.937563863588373</v>
       </c>
       <c r="E13">
-        <v>-29.49307929318116</v>
+        <v>-35.80636528996865</v>
       </c>
       <c r="F13">
-        <v>-3.462977649139799</v>
+        <v>-4.392216178945604</v>
       </c>
       <c r="G13">
-        <v>-13.63878666335777</v>
+        <v>-17.28820460984706</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.087846229909368</v>
       </c>
       <c r="E14">
-        <v>-30.38659702810861</v>
+        <v>-36.71295899359324</v>
       </c>
       <c r="F14">
-        <v>-3.158606472492163</v>
+        <v>-4.374362376313066</v>
       </c>
       <c r="G14">
-        <v>-13.05019152974859</v>
+        <v>-16.95423181002708</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.311359476754688</v>
       </c>
       <c r="E15">
-        <v>-31.12778369012903</v>
+        <v>-37.12339044256743</v>
       </c>
       <c r="F15">
-        <v>-2.932369394378784</v>
+        <v>-4.288690962780735</v>
       </c>
       <c r="G15">
-        <v>-12.77179782371466</v>
+        <v>-16.59951513185802</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6365851225059374</v>
       </c>
       <c r="E16">
-        <v>-31.01829198133457</v>
+        <v>-37.01059294774737</v>
       </c>
       <c r="F16">
-        <v>-2.826554570712578</v>
+        <v>-4.029906501043961</v>
       </c>
       <c r="G16">
-        <v>-12.58095149446675</v>
+        <v>-16.61051276413948</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.09291446449720006</v>
       </c>
       <c r="E17">
-        <v>-32.20395063144485</v>
+        <v>-38.01914750789167</v>
       </c>
       <c r="F17">
-        <v>-2.768596188640905</v>
+        <v>-4.099884494130255</v>
       </c>
       <c r="G17">
-        <v>-12.15664549378944</v>
+        <v>-16.49474133135839</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.3076544103104666</v>
       </c>
       <c r="E18">
-        <v>-32.67237598279827</v>
+        <v>-38.12772672917358</v>
       </c>
       <c r="F18">
-        <v>-2.521418810952158</v>
+        <v>-3.805356807330085</v>
       </c>
       <c r="G18">
-        <v>-11.94426075526304</v>
+        <v>-16.20446442211125</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.5663219417048914</v>
       </c>
       <c r="E19">
-        <v>-33.323409784274</v>
+        <v>-38.66786952338648</v>
       </c>
       <c r="F19">
-        <v>-2.490496684173055</v>
+        <v>-3.725550235009575</v>
       </c>
       <c r="G19">
-        <v>-12.04342152580083</v>
+        <v>-16.1027230813256</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.6857764572300709</v>
       </c>
       <c r="E20">
-        <v>-33.70542958732406</v>
+        <v>-39.88681472169014</v>
       </c>
       <c r="F20">
-        <v>-2.179237632571141</v>
+        <v>-3.57705543764893</v>
       </c>
       <c r="G20">
-        <v>-11.75777772503589</v>
+        <v>-15.96329283484811</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.680432743948825</v>
       </c>
       <c r="E21">
-        <v>-35.00653941802289</v>
+        <v>-39.88095261208721</v>
       </c>
       <c r="F21">
-        <v>-2.156904847391666</v>
+        <v>-3.447251922365053</v>
       </c>
       <c r="G21">
-        <v>-11.95591056501573</v>
+        <v>-15.5966350189189</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.5722807934268149</v>
       </c>
       <c r="E22">
-        <v>-35.01589750955974</v>
+        <v>-40.53228076437343</v>
       </c>
       <c r="F22">
-        <v>-1.977558334481156</v>
+        <v>-3.222351829239793</v>
       </c>
       <c r="G22">
-        <v>-11.62255518193882</v>
+        <v>-15.53633343192108</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.3807007956124867</v>
       </c>
       <c r="E23">
-        <v>-35.28462394988591</v>
+        <v>-41.11628182935061</v>
       </c>
       <c r="F23">
-        <v>-1.823997242084989</v>
+        <v>-3.262750479106922</v>
       </c>
       <c r="G23">
-        <v>-11.51783600544059</v>
+        <v>-15.28235996505758</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.1275974757878874</v>
       </c>
       <c r="E24">
-        <v>-35.55199411224679</v>
+        <v>-41.0817341011461</v>
       </c>
       <c r="F24">
-        <v>-1.779693668281064</v>
+        <v>-2.942631209764664</v>
       </c>
       <c r="G24">
-        <v>-11.71172472603909</v>
+        <v>-15.36481406753144</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.164869108034642</v>
       </c>
       <c r="E25">
-        <v>-36.0351166259921</v>
+        <v>-40.90843845782057</v>
       </c>
       <c r="F25">
-        <v>-1.627579733737588</v>
+        <v>-2.975180250122865</v>
       </c>
       <c r="G25">
-        <v>-11.40026529115892</v>
+        <v>-15.79606724802291</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.4825348150437117</v>
       </c>
       <c r="E26">
-        <v>-36.45050448976769</v>
+        <v>-41.19295795124849</v>
       </c>
       <c r="F26">
-        <v>-1.558649625415835</v>
+        <v>-3.097102677936508</v>
       </c>
       <c r="G26">
-        <v>-11.4837704918415</v>
+        <v>-15.4679938403539</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8133023714043415</v>
       </c>
       <c r="E27">
-        <v>-36.36817230383424</v>
+        <v>-41.07662371822844</v>
       </c>
       <c r="F27">
-        <v>-1.576489345802525</v>
+        <v>-2.978535138104203</v>
       </c>
       <c r="G27">
-        <v>-11.38533804132234</v>
+        <v>-15.43476423950347</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.146077139503187</v>
       </c>
       <c r="E28">
-        <v>-36.2051472395581</v>
+        <v>-41.22057937845828</v>
       </c>
       <c r="F28">
-        <v>-1.457683236158215</v>
+        <v>-2.959018802094247</v>
       </c>
       <c r="G28">
-        <v>-11.73796410998335</v>
+        <v>-16.13760298912736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.477539995715432</v>
       </c>
       <c r="E29">
-        <v>-36.16123009863171</v>
+        <v>-41.38481128105745</v>
       </c>
       <c r="F29">
-        <v>-1.427871121698863</v>
+        <v>-3.08466391301607</v>
       </c>
       <c r="G29">
-        <v>-11.62783219152842</v>
+        <v>-15.49661516181367</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.804676246551332</v>
       </c>
       <c r="E30">
-        <v>-35.94808388403869</v>
+        <v>-41.41668041688643</v>
       </c>
       <c r="F30">
-        <v>-1.416358471534756</v>
+        <v>-2.75016335719381</v>
       </c>
       <c r="G30">
-        <v>-11.65863681777134</v>
+        <v>-15.64144490806571</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.122236456308148</v>
       </c>
       <c r="E31">
-        <v>-35.66149487798926</v>
+        <v>-41.07885399167721</v>
       </c>
       <c r="F31">
-        <v>-1.461814304395976</v>
+        <v>-2.778620262582182</v>
       </c>
       <c r="G31">
-        <v>-11.46630074303076</v>
+        <v>-16.17662769994429</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.431515299376217</v>
       </c>
       <c r="E32">
-        <v>-35.13178568789004</v>
+        <v>-40.81854824876831</v>
       </c>
       <c r="F32">
-        <v>-1.639444440047885</v>
+        <v>-3.071363645996721</v>
       </c>
       <c r="G32">
-        <v>-11.88457824028106</v>
+        <v>-15.79744940078555</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.731946642093221</v>
       </c>
       <c r="E33">
-        <v>-35.19974902579715</v>
+        <v>-40.45434119822741</v>
       </c>
       <c r="F33">
-        <v>-1.618512424146544</v>
+        <v>-3.145622641820683</v>
       </c>
       <c r="G33">
-        <v>-11.70367016874204</v>
+        <v>-16.07766887268439</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.019267930528428</v>
       </c>
       <c r="E34">
-        <v>-34.79358339933819</v>
+        <v>-40.01690419450848</v>
       </c>
       <c r="F34">
-        <v>-1.541451889766315</v>
+        <v>-2.852602583693609</v>
       </c>
       <c r="G34">
-        <v>-12.23039120622225</v>
+        <v>-16.07200783981224</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.294956993012702</v>
       </c>
       <c r="E35">
-        <v>-34.02737238995137</v>
+        <v>-39.92751891030808</v>
       </c>
       <c r="F35">
-        <v>-1.628925830767137</v>
+        <v>-2.920310850096232</v>
       </c>
       <c r="G35">
-        <v>-12.30040262328675</v>
+        <v>-16.24232713144389</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.558176640363589</v>
       </c>
       <c r="E36">
-        <v>-34.1094487171034</v>
+        <v>-39.71608219465295</v>
       </c>
       <c r="F36">
-        <v>-1.59057242001752</v>
+        <v>-2.981759972403302</v>
       </c>
       <c r="G36">
-        <v>-12.32059364053077</v>
+        <v>-16.29572126517403</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.803468469936165</v>
       </c>
       <c r="E37">
-        <v>-33.98759880274201</v>
+        <v>-39.41316577556886</v>
       </c>
       <c r="F37">
-        <v>-1.566793305352757</v>
+        <v>-2.806146083009807</v>
       </c>
       <c r="G37">
-        <v>-11.94207579520712</v>
+        <v>-15.9486403602913</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.02882742368278</v>
       </c>
       <c r="E38">
-        <v>-33.17724422872842</v>
+        <v>-38.75417544526166</v>
       </c>
       <c r="F38">
-        <v>-1.546865270743609</v>
+        <v>-3.004542561082497</v>
       </c>
       <c r="G38">
-        <v>-11.95201736346155</v>
+        <v>-16.55125896480483</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.233442032777982</v>
       </c>
       <c r="E39">
-        <v>-33.16661590023242</v>
+        <v>-38.47697849430414</v>
       </c>
       <c r="F39">
-        <v>-1.546254763967746</v>
+        <v>-2.951119490541151</v>
       </c>
       <c r="G39">
-        <v>-12.21364315633907</v>
+        <v>-16.16530894474552</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.412568680404157</v>
       </c>
       <c r="E40">
-        <v>-32.99375725464863</v>
+        <v>-37.97077208430473</v>
       </c>
       <c r="F40">
-        <v>-1.583305981160162</v>
+        <v>-3.029531092155346</v>
       </c>
       <c r="G40">
-        <v>-12.21774161171669</v>
+        <v>-16.07988528292293</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.563300961160815</v>
       </c>
       <c r="E41">
-        <v>-32.43604398128597</v>
+        <v>-37.29384673269015</v>
       </c>
       <c r="F41">
-        <v>-1.554521042280282</v>
+        <v>-2.880482945369631</v>
       </c>
       <c r="G41">
-        <v>-12.20915405658782</v>
+        <v>-16.46871382232865</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.687518201118821</v>
       </c>
       <c r="E42">
-        <v>-31.52556031848879</v>
+        <v>-37.42179650153987</v>
       </c>
       <c r="F42">
-        <v>-1.484236553254953</v>
+        <v>-2.85512993263955</v>
       </c>
       <c r="G42">
-        <v>-12.12173579107783</v>
+        <v>-16.46810468194942</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.784779451134348</v>
       </c>
       <c r="E43">
-        <v>-30.88817533767218</v>
+        <v>-36.81379678855904</v>
       </c>
       <c r="F43">
-        <v>-1.421201107371522</v>
+        <v>-2.792039814507534</v>
       </c>
       <c r="G43">
-        <v>-12.49472502535089</v>
+        <v>-16.36632858043561</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.85461157898017</v>
       </c>
       <c r="E44">
-        <v>-30.93514014160573</v>
+        <v>-36.18018629082782</v>
       </c>
       <c r="F44">
-        <v>-1.513087761527057</v>
+        <v>-2.865316366591775</v>
       </c>
       <c r="G44">
-        <v>-12.35482799195237</v>
+        <v>-16.02715325830065</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.903661892349382</v>
       </c>
       <c r="E45">
-        <v>-29.94984608820183</v>
+        <v>-35.57381456425275</v>
       </c>
       <c r="F45">
-        <v>-1.480082290729913</v>
+        <v>-2.957448217498539</v>
       </c>
       <c r="G45">
-        <v>-12.1137673079648</v>
+        <v>-16.36804344302495</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.937647317368178</v>
       </c>
       <c r="E46">
-        <v>-29.67885088239782</v>
+        <v>-35.44080875417346</v>
       </c>
       <c r="F46">
-        <v>-1.420023168924741</v>
+        <v>-2.802513691948531</v>
       </c>
       <c r="G46">
-        <v>-12.51538614006149</v>
+        <v>-16.67816210696171</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.95905573339504</v>
       </c>
       <c r="E47">
-        <v>-29.45124072182429</v>
+        <v>-35.0822305968241</v>
       </c>
       <c r="F47">
-        <v>-1.542238838798974</v>
+        <v>-2.729875811131848</v>
       </c>
       <c r="G47">
-        <v>-12.01880430917081</v>
+        <v>-16.55687365003944</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.979015402799296</v>
       </c>
       <c r="E48">
-        <v>-28.97564679611673</v>
+        <v>-34.45212513797483</v>
       </c>
       <c r="F48">
-        <v>-1.469555397775137</v>
+        <v>-2.795028564096834</v>
       </c>
       <c r="G48">
-        <v>-12.14804469647842</v>
+        <v>-16.29044756612997</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.009321355934102</v>
       </c>
       <c r="E49">
-        <v>-28.75828910069657</v>
+        <v>-34.48354142640304</v>
       </c>
       <c r="F49">
-        <v>-1.395851408111051</v>
+        <v>-2.686989573954112</v>
       </c>
       <c r="G49">
-        <v>-11.97711129864923</v>
+        <v>-16.60891873646232</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.05425563096396</v>
       </c>
       <c r="E50">
-        <v>-28.11523220618535</v>
+        <v>-34.2471324408326</v>
       </c>
       <c r="F50">
-        <v>-1.407301930719949</v>
+        <v>-2.682074041785899</v>
       </c>
       <c r="G50">
-        <v>-12.12147756852576</v>
+        <v>-16.52302166662762</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.125298470194471</v>
       </c>
       <c r="E51">
-        <v>-27.80764919463637</v>
+        <v>-33.42362264982674</v>
       </c>
       <c r="F51">
-        <v>-1.291903724570755</v>
+        <v>-2.798163106349028</v>
       </c>
       <c r="G51">
-        <v>-12.29834677450687</v>
+        <v>-16.54471401627369</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.233961604294787</v>
       </c>
       <c r="E52">
-        <v>-27.17104537558608</v>
+        <v>-33.23277011277347</v>
       </c>
       <c r="F52">
-        <v>-1.525656580129734</v>
+        <v>-2.773599527753814</v>
       </c>
       <c r="G52">
-        <v>-11.97254605635057</v>
+        <v>-16.93540970336355</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.377633952196453</v>
       </c>
       <c r="E53">
-        <v>-26.5049249629538</v>
+        <v>-33.25768351252667</v>
       </c>
       <c r="F53">
-        <v>-1.342314022868119</v>
+        <v>-2.736557422602829</v>
       </c>
       <c r="G53">
-        <v>-12.54039731161068</v>
+        <v>-16.87669883349735</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.560193241012063</v>
       </c>
       <c r="E54">
-        <v>-26.33067834008666</v>
+        <v>-32.2976153235825</v>
       </c>
       <c r="F54">
-        <v>-1.419404378474849</v>
+        <v>-2.697762492027519</v>
       </c>
       <c r="G54">
-        <v>-12.15939324658704</v>
+        <v>-16.51603807081253</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.786786978571946</v>
       </c>
       <c r="E55">
-        <v>-26.42557704139141</v>
+        <v>-32.22699377143288</v>
       </c>
       <c r="F55">
-        <v>-1.489562955654953</v>
+        <v>-2.914639018489264</v>
       </c>
       <c r="G55">
-        <v>-12.48273422940765</v>
+        <v>-16.86733330016675</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.047708334695349</v>
       </c>
       <c r="E56">
-        <v>-25.49151587867329</v>
+        <v>-31.91277880969966</v>
       </c>
       <c r="F56">
-        <v>-1.345266324291696</v>
+        <v>-2.668760520888106</v>
       </c>
       <c r="G56">
-        <v>-12.52151064930914</v>
+        <v>-16.66284255747874</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.338296923000476</v>
       </c>
       <c r="E57">
-        <v>-24.51269527886335</v>
+        <v>-31.65651925831661</v>
       </c>
       <c r="F57">
-        <v>-1.155575987622429</v>
+        <v>-2.735021629438038</v>
       </c>
       <c r="G57">
-        <v>-12.78832737759224</v>
+        <v>-16.74903757641197</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.658023642222703</v>
       </c>
       <c r="E58">
-        <v>-24.78788611583547</v>
+        <v>-31.13323823707127</v>
       </c>
       <c r="F58">
-        <v>-1.438581083849658</v>
+        <v>-2.884092142143629</v>
       </c>
       <c r="G58">
-        <v>-12.3214643140076</v>
+        <v>-16.96330436007745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.994530904296812</v>
       </c>
       <c r="E59">
-        <v>-24.61807739749585</v>
+        <v>-31.31591687854069</v>
       </c>
       <c r="F59">
-        <v>-1.35925744972498</v>
+        <v>-2.718108023807678</v>
       </c>
       <c r="G59">
-        <v>-12.65120789190116</v>
+        <v>-16.78935339998922</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.338318887084367</v>
       </c>
       <c r="E60">
-        <v>-24.31834675987616</v>
+        <v>-30.60846961211442</v>
       </c>
       <c r="F60">
-        <v>-1.515329323719032</v>
+        <v>-2.807297513699698</v>
       </c>
       <c r="G60">
-        <v>-12.6846444018478</v>
+        <v>-17.3189645437252</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.687611406395096</v>
       </c>
       <c r="E61">
-        <v>-24.45471722614315</v>
+        <v>-30.7259495490584</v>
       </c>
       <c r="F61">
-        <v>-1.552822889104543</v>
+        <v>-2.86543896496739</v>
       </c>
       <c r="G61">
-        <v>-12.56496487005761</v>
+        <v>-16.83919862890125</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.031825602446068</v>
       </c>
       <c r="E62">
-        <v>-23.5982741079165</v>
+        <v>-30.63054592290181</v>
       </c>
       <c r="F62">
-        <v>-1.55255863990305</v>
+        <v>-2.897968124507923</v>
       </c>
       <c r="G62">
-        <v>-12.70236244157398</v>
+        <v>-17.13348460879646</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.358958421468596</v>
       </c>
       <c r="E63">
-        <v>-23.74364718051073</v>
+        <v>-30.70794660064091</v>
       </c>
       <c r="F63">
-        <v>-1.600209646381689</v>
+        <v>-2.971812936630486</v>
       </c>
       <c r="G63">
-        <v>-12.86569482684501</v>
+        <v>-16.95887485014591</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.667179008706784</v>
       </c>
       <c r="E64">
-        <v>-24.08264874472494</v>
+        <v>-30.32789894802118</v>
       </c>
       <c r="F64">
-        <v>-1.583468341171111</v>
+        <v>-2.739683681180994</v>
       </c>
       <c r="G64">
-        <v>-12.77166209134755</v>
+        <v>-17.1811978463812</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.949377451071225</v>
       </c>
       <c r="E65">
-        <v>-23.52592267869595</v>
+        <v>-30.24758646149515</v>
       </c>
       <c r="F65">
-        <v>-1.747166993842738</v>
+        <v>-2.965879340924233</v>
       </c>
       <c r="G65">
-        <v>-12.76770598942812</v>
+        <v>-17.47688418703952</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.193521709668088</v>
       </c>
       <c r="E66">
-        <v>-22.99309337000544</v>
+        <v>-29.90784222754369</v>
       </c>
       <c r="F66">
-        <v>-1.742143773912162</v>
+        <v>-3.130446122633993</v>
       </c>
       <c r="G66">
-        <v>-12.75179550756638</v>
+        <v>-17.27521568442373</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.399301692450251</v>
       </c>
       <c r="E67">
-        <v>-23.43144965394793</v>
+        <v>-30.08545350659853</v>
       </c>
       <c r="F67">
-        <v>-1.989711312647628</v>
+        <v>-3.319144075154707</v>
       </c>
       <c r="G67">
-        <v>-12.96792116255216</v>
+        <v>-17.32113129578066</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.565030455618968</v>
       </c>
       <c r="E68">
-        <v>-23.6345200138739</v>
+        <v>-29.94655615183526</v>
       </c>
       <c r="F68">
-        <v>-1.767620213385261</v>
+        <v>-3.263867946733299</v>
       </c>
       <c r="G68">
-        <v>-12.79153529621979</v>
+        <v>-16.81514917083122</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.680681052984717</v>
       </c>
       <c r="E69">
-        <v>-22.73302763621894</v>
+        <v>-30.02824529445963</v>
       </c>
       <c r="F69">
-        <v>-2.071209411204654</v>
+        <v>-3.183478203761218</v>
       </c>
       <c r="G69">
-        <v>-12.61139527124589</v>
+        <v>-16.96803844019861</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.747381320512506</v>
       </c>
       <c r="E70">
-        <v>-22.86364694049619</v>
+        <v>-30.06230621170832</v>
       </c>
       <c r="F70">
-        <v>-2.01163488433012</v>
+        <v>-3.435952990990868</v>
       </c>
       <c r="G70">
-        <v>-12.82439246069706</v>
+        <v>-17.12476628711878</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.769153021269856</v>
       </c>
       <c r="E71">
-        <v>-22.92108610480948</v>
+        <v>-29.98901285989417</v>
       </c>
       <c r="F71">
-        <v>-2.171193356722555</v>
+        <v>-3.425050019235221</v>
       </c>
       <c r="G71">
-        <v>-12.79560064614202</v>
+        <v>-16.96339540007978</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.738325537362135</v>
       </c>
       <c r="E72">
-        <v>-23.23894422388187</v>
+        <v>-30.4024149878174</v>
       </c>
       <c r="F72">
-        <v>-2.468672516578899</v>
+        <v>-3.438920203027696</v>
       </c>
       <c r="G72">
-        <v>-12.42033044599239</v>
+        <v>-16.86223009421796</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.655736127302003</v>
       </c>
       <c r="E73">
-        <v>-23.18713395276011</v>
+        <v>-29.57389896879605</v>
       </c>
       <c r="F73">
-        <v>-2.283042008550753</v>
+        <v>-3.640718786023683</v>
       </c>
       <c r="G73">
-        <v>-12.57099668403016</v>
+        <v>-17.03872024273482</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.530980306104015</v>
       </c>
       <c r="E74">
-        <v>-23.05611614277019</v>
+        <v>-30.00503233669631</v>
       </c>
       <c r="F74">
-        <v>-2.397308664827722</v>
+        <v>-3.63912003693628</v>
       </c>
       <c r="G74">
-        <v>-12.1769325168541</v>
+        <v>-16.65505284382483</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.360709448772761</v>
       </c>
       <c r="E75">
-        <v>-23.25294173703957</v>
+        <v>-30.37450147403412</v>
       </c>
       <c r="F75">
-        <v>-2.546680703267931</v>
+        <v>-3.523516395671193</v>
       </c>
       <c r="G75">
-        <v>-12.35483461304345</v>
+        <v>-16.71178897327686</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.147765210008663</v>
       </c>
       <c r="E76">
-        <v>-23.49131608032934</v>
+        <v>-30.21989031446424</v>
       </c>
       <c r="F76">
-        <v>-2.737728734110387</v>
+        <v>-3.82470415638987</v>
       </c>
       <c r="G76">
-        <v>-12.14516121131371</v>
+        <v>-16.76097871417212</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.906065553168846</v>
       </c>
       <c r="E77">
-        <v>-23.8718573366159</v>
+        <v>-30.48099986150951</v>
       </c>
       <c r="F77">
-        <v>-2.892553915163226</v>
+        <v>-3.939100037981676</v>
       </c>
       <c r="G77">
-        <v>-12.18164673370202</v>
+        <v>-16.51648830500587</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.638023366360562</v>
       </c>
       <c r="E78">
-        <v>-24.19434808459814</v>
+        <v>-30.93468502996796</v>
       </c>
       <c r="F78">
-        <v>-2.904442644128205</v>
+        <v>-3.94587111313216</v>
       </c>
       <c r="G78">
-        <v>-11.74539628471902</v>
+        <v>-16.38630441221957</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.347815675031228</v>
       </c>
       <c r="E79">
-        <v>-23.88136713203201</v>
+        <v>-30.84143922167602</v>
       </c>
       <c r="F79">
-        <v>-2.755773061245569</v>
+        <v>-4.116378117487396</v>
       </c>
       <c r="G79">
-        <v>-12.11629325421127</v>
+        <v>-16.17020689687087</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.052388511909275</v>
       </c>
       <c r="E80">
-        <v>-24.83864578098745</v>
+        <v>-31.24351563610606</v>
       </c>
       <c r="F80">
-        <v>-2.983640366407657</v>
+        <v>-3.998143581351017</v>
       </c>
       <c r="G80">
-        <v>-11.57804820770886</v>
+        <v>-16.21343103470436</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.759821730991889</v>
       </c>
       <c r="E81">
-        <v>-25.06338036056611</v>
+        <v>-31.72443957572065</v>
       </c>
       <c r="F81">
-        <v>-2.932270818657851</v>
+        <v>-4.130947443367834</v>
       </c>
       <c r="G81">
-        <v>-11.23277486069057</v>
+        <v>-15.96180639990098</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.475831333521952</v>
       </c>
       <c r="E82">
-        <v>-25.43244193524323</v>
+        <v>-31.93384527078334</v>
       </c>
       <c r="F82">
-        <v>-2.718128732992748</v>
+        <v>-3.930825475995112</v>
       </c>
       <c r="G82">
-        <v>-11.16358776946534</v>
+        <v>-16.26739292699449</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.218746628555723</v>
       </c>
       <c r="E83">
-        <v>-26.0355667459548</v>
+        <v>-32.27363478947488</v>
       </c>
       <c r="F83">
-        <v>-2.901932690897722</v>
+        <v>-4.222607953222404</v>
       </c>
       <c r="G83">
-        <v>-11.0267827856005</v>
+        <v>-16.09535049640964</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.000907918937824</v>
       </c>
       <c r="E84">
-        <v>-26.89064226503114</v>
+        <v>-33.03315045004135</v>
       </c>
       <c r="F84">
-        <v>-3.250110420907605</v>
+        <v>-4.039870104164834</v>
       </c>
       <c r="G84">
-        <v>-10.99317743783136</v>
+        <v>-15.94472398491834</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.826984466172249</v>
       </c>
       <c r="E85">
-        <v>-27.25323265035129</v>
+        <v>-33.68140603271338</v>
       </c>
       <c r="F85">
-        <v>-3.049411909822535</v>
+        <v>-4.128020821333743</v>
       </c>
       <c r="G85">
-        <v>-10.8409022746615</v>
+        <v>-15.63523929045234</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.712040003444788</v>
       </c>
       <c r="E86">
-        <v>-27.88121425489097</v>
+        <v>-34.0799298592844</v>
       </c>
       <c r="F86">
-        <v>-3.169415010363891</v>
+        <v>-4.367707272598974</v>
       </c>
       <c r="G86">
-        <v>-10.59311456213813</v>
+        <v>-15.80603033482334</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.666182175704972</v>
       </c>
       <c r="E87">
-        <v>-29.55944407976357</v>
+        <v>-34.75159538833907</v>
       </c>
       <c r="F87">
-        <v>-3.201134854951889</v>
+        <v>-4.381816026203455</v>
       </c>
       <c r="G87">
-        <v>-10.98794015478823</v>
+        <v>-15.97405872894182</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.685765995009901</v>
       </c>
       <c r="E88">
-        <v>-30.24407915837621</v>
+        <v>-35.56384286448786</v>
       </c>
       <c r="F88">
-        <v>-3.136724319179811</v>
+        <v>-4.18542419724554</v>
       </c>
       <c r="G88">
-        <v>-10.53082995836228</v>
+        <v>-15.26683185120563</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.775876168210887</v>
       </c>
       <c r="E89">
-        <v>-31.08731498215949</v>
+        <v>-36.39534314788025</v>
       </c>
       <c r="F89">
-        <v>-3.18723982013733</v>
+        <v>-4.475576447424123</v>
       </c>
       <c r="G89">
-        <v>-10.55762220341161</v>
+        <v>-15.59777715712995</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.93999788284939</v>
       </c>
       <c r="E90">
-        <v>-32.28206454384016</v>
+        <v>-37.4895311515096</v>
       </c>
       <c r="F90">
-        <v>-3.159645245215273</v>
+        <v>-4.616533929786695</v>
       </c>
       <c r="G90">
-        <v>-10.75377533715896</v>
+        <v>-15.90155447108624</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.164124895726701</v>
       </c>
       <c r="E91">
-        <v>-33.58621977330915</v>
+        <v>-38.31056613147027</v>
       </c>
       <c r="F91">
-        <v>-3.395462392342028</v>
+        <v>-4.501036319549166</v>
       </c>
       <c r="G91">
-        <v>-10.88559132889612</v>
+        <v>-15.4410807603924</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.442656512472312</v>
       </c>
       <c r="E92">
-        <v>-34.81691636166271</v>
+        <v>-39.54287259233356</v>
       </c>
       <c r="F92">
-        <v>-3.636615053910214</v>
+        <v>-4.549070031767898</v>
       </c>
       <c r="G92">
-        <v>-10.61675516783407</v>
+        <v>-15.72990268487503</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.772017235981203</v>
       </c>
       <c r="E93">
-        <v>-35.72958274893159</v>
+        <v>-40.33566121567139</v>
       </c>
       <c r="F93">
-        <v>-3.76122801904815</v>
+        <v>-4.783937869851044</v>
       </c>
       <c r="G93">
-        <v>-11.06377151091078</v>
+        <v>-16.05317414623932</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.128598580986392</v>
       </c>
       <c r="E94">
-        <v>-37.57895945621308</v>
+        <v>-41.27972804170946</v>
       </c>
       <c r="F94">
-        <v>-3.567212776168867</v>
+        <v>-4.848179418672951</v>
       </c>
       <c r="G94">
-        <v>-11.23893247539362</v>
+        <v>-15.804947786432</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.498633088417074</v>
       </c>
       <c r="E95">
-        <v>-39.09230074975538</v>
+        <v>-42.78003185858368</v>
       </c>
       <c r="F95">
-        <v>-3.708961349401112</v>
+        <v>-4.946388172846653</v>
       </c>
       <c r="G95">
-        <v>-11.40171199955958</v>
+        <v>-15.69019600167701</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.869449617575713</v>
       </c>
       <c r="E96">
-        <v>-40.50972443534122</v>
+        <v>-44.41424718033873</v>
       </c>
       <c r="F96">
-        <v>-3.795713782394096</v>
+        <v>-5.030443441576121</v>
       </c>
       <c r="G96">
-        <v>-11.49908176496062</v>
+        <v>-16.07543425444538</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.215481010016195</v>
       </c>
       <c r="E97">
-        <v>-42.19675534944773</v>
+        <v>-45.72680725756595</v>
       </c>
       <c r="F97">
-        <v>-3.849353885194975</v>
+        <v>-5.325697606588546</v>
       </c>
       <c r="G97">
-        <v>-11.96970229773234</v>
+        <v>-16.96978806351611</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.511046616780554</v>
       </c>
       <c r="E98">
-        <v>-43.6505653236852</v>
+        <v>-47.046350241713</v>
       </c>
       <c r="F98">
-        <v>-4.027801619473448</v>
+        <v>-5.058817510224213</v>
       </c>
       <c r="G98">
-        <v>-12.03890594168526</v>
+        <v>-16.52123893785472</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.74904620062366</v>
       </c>
       <c r="E99">
-        <v>-45.60032697853172</v>
+        <v>-48.59461965527647</v>
       </c>
       <c r="F99">
-        <v>-4.173769067888151</v>
+        <v>-5.2038331644931</v>
       </c>
       <c r="G99">
-        <v>-12.07093215923217</v>
+        <v>-16.93217033455338</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.896590119044099</v>
       </c>
       <c r="E100">
-        <v>-46.93478449182303</v>
+        <v>-49.98614726224945</v>
       </c>
       <c r="F100">
-        <v>-4.214748403304642</v>
+        <v>-5.617300328089431</v>
       </c>
       <c r="G100">
-        <v>-12.56752723230501</v>
+        <v>-17.36860286354104</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.950870091363404</v>
       </c>
       <c r="E101">
-        <v>-49.32509194779475</v>
+        <v>-51.50569709365627</v>
       </c>
       <c r="F101">
-        <v>-4.321085098434613</v>
+        <v>-5.634509660882591</v>
       </c>
       <c r="G101">
-        <v>-12.89003064710419</v>
+        <v>-17.38057710675658</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.881012302452731</v>
       </c>
       <c r="E102">
-        <v>-51.1472321481571</v>
+        <v>-53.38133328958973</v>
       </c>
       <c r="F102">
-        <v>-4.377513485913314</v>
+        <v>-5.584436508118166</v>
       </c>
       <c r="G102">
-        <v>-13.03885291127659</v>
+        <v>-17.17329722945173</v>
       </c>
     </row>
   </sheetData>
